--- a/base_despesas/2026/despesas_202601.xlsx
+++ b/base_despesas/2026/despesas_202601.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF149"/>
+  <dimension ref="A1:AG150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,15 +564,20 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>acao_programatica</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>nome_elemento</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>ds_fonte</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>nome_elemento</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>data_hora_extracao</t>
         </is>
@@ -682,17 +687,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>Conselho</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Material de Consumo</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUNDO MUNICIPAL DO IDOSO-FMID</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Material de Consumo</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>31/01/2026 08:28:52</t>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -800,17 +810,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>FMID</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUNDO MUNICIPAL DO IDOSO-FMID</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>31/01/2026 08:28:52</t>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -918,7 +933,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Formação</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -928,7 +943,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1056,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1046,7 +1066,12 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1179,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1164,7 +1189,12 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1302,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1282,7 +1312,12 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1425,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1400,7 +1435,12 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1548,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1518,7 +1558,12 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1671,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1636,7 +1681,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1794,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>31/01/2026 08:28:52</t>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1917,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -1872,7 +1927,12 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2040,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -1990,7 +2050,12 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2163,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2108,7 +2173,12 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2286,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2226,7 +2296,12 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2409,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2344,7 +2419,12 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2532,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM - CIEE</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -2462,7 +2542,12 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2655,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -2580,7 +2665,12 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2778,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -2698,7 +2788,12 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2901,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -2816,7 +2911,12 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -2924,7 +3024,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia - Comunicação</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -2934,7 +3034,12 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3147,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia - Comunicação</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3052,7 +3157,12 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3270,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia - Comunicação</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3170,7 +3280,12 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3393,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3288,7 +3403,12 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3516,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -3406,7 +3526,12 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3639,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -3524,7 +3649,12 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3762,7 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3642,7 +3772,12 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3885,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -3760,7 +3895,12 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3868,7 +4008,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -3878,7 +4018,12 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -3986,7 +4131,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -3996,7 +4141,12 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4104,17 +4254,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
+          <t>CT - Administração</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>31/01/2026 08:28:52</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4377,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -4232,7 +4387,12 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4500,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -4350,7 +4510,12 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4623,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -4468,7 +4633,12 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4746,7 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -4586,7 +4756,12 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4869,7 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -4704,7 +4879,12 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4992,7 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Cooperação Técnica Internacional</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
@@ -4822,7 +5002,12 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -4930,7 +5115,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -4940,7 +5125,12 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5048,17 +5238,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
+          <t>Sesana - Políticas</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
           <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>31/01/2026 08:28:52</t>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5285,7 @@
         <v>4010</v>
       </c>
       <c r="G40" t="n">
-        <v>4470</v>
+        <v>4426</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5099,12 +5294,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -5126,34 +5321,34 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6558</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>6558</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>10494</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>6558</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3936</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>77329</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>22671</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>5</v>
@@ -5166,17 +5361,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5417,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5244,34 +5444,34 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>6558</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>6558</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>10494</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>6558</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3936</v>
       </c>
       <c r="V41" t="n">
-        <v>635623</v>
+        <v>77329</v>
       </c>
       <c r="W41" t="n">
-        <v>821969</v>
+        <v>100000</v>
       </c>
       <c r="X41" t="n">
-        <v>186346</v>
+        <v>22671</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>821969</v>
+        <v>100000</v>
       </c>
       <c r="AA41" t="n">
         <v>5</v>
@@ -5284,17 +5484,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5540,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5362,34 +5567,34 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1087620.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>450875.94</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>450875.94</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1087620.9</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>16294924</v>
+        <v>635623</v>
       </c>
       <c r="W42" t="n">
-        <v>21072104</v>
+        <v>821969</v>
       </c>
       <c r="X42" t="n">
-        <v>4777180</v>
+        <v>186346</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>21072104</v>
+        <v>821969</v>
       </c>
       <c r="AA42" t="n">
         <v>5</v>
@@ -5402,17 +5607,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5668,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -5480,34 +5690,34 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>316616</v>
+        <v>1087620.9</v>
       </c>
       <c r="R43" t="n">
-        <v>316616</v>
+        <v>450875.94</v>
       </c>
       <c r="S43" t="n">
-        <v>316616</v>
+        <v>450875.94</v>
       </c>
       <c r="T43" t="n">
-        <v>316616</v>
+        <v>1087620.9</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>316616</v>
+        <v>16294924</v>
       </c>
       <c r="W43" t="n">
-        <v>316616</v>
+        <v>21072104</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4777180</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>316616</v>
+        <v>21072104</v>
       </c>
       <c r="AA43" t="n">
         <v>5</v>
@@ -5520,7 +5730,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -5530,7 +5740,12 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5786,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -5598,25 +5813,25 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>28666</v>
+        <v>316616</v>
       </c>
       <c r="W44" t="n">
-        <v>28666</v>
+        <v>316616</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -5625,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>28666</v>
+        <v>316616</v>
       </c>
       <c r="AA44" t="n">
         <v>5</v>
@@ -5638,17 +5853,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5900,7 @@
         <v>4010</v>
       </c>
       <c r="G45" t="n">
-        <v>7001</v>
+        <v>4470</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5689,7 +5909,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>44903900</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5731,10 +5951,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1000</v>
+        <v>28666</v>
       </c>
       <c r="W45" t="n">
-        <v>1000</v>
+        <v>28666</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -5743,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>28666</v>
       </c>
       <c r="AA45" t="n">
         <v>5</v>
@@ -5756,17 +5976,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>Material Permanente</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5795,19 +6020,19 @@
         <v>422</v>
       </c>
       <c r="F46" t="n">
-        <v>4018</v>
+        <v>4010</v>
       </c>
       <c r="G46" t="n">
-        <v>2431</v>
+        <v>7001</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CPPSR</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44903900</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5828,40 +6053,40 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4140329.7</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13165012.7</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>9024683</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>11429605.99</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>9024683</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2404922.99</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>9024683</v>
+        <v>1000</v>
       </c>
       <c r="W46" t="n">
-        <v>10590662</v>
+        <v>1000</v>
       </c>
       <c r="X46" t="n">
-        <v>1565979</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>10590662</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
         <v>5</v>
@@ -5869,22 +6094,27 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>População em Situação de Rua</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Material Permanente</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -5925,7 +6155,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5946,40 +6176,40 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4140329.7</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>13165012.7</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>9024683</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>11429605.99</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>9024683</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2404922.99</v>
       </c>
       <c r="V47" t="n">
-        <v>249936</v>
+        <v>9024683</v>
       </c>
       <c r="W47" t="n">
-        <v>293305</v>
+        <v>10590662</v>
       </c>
       <c r="X47" t="n">
-        <v>43369</v>
+        <v>1565979</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>293305</v>
+        <v>10590662</v>
       </c>
       <c r="AA47" t="n">
         <v>5</v>
@@ -5992,17 +6222,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Equipamentos</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6278,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6085,19 +6320,19 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>86656</v>
+        <v>249936</v>
       </c>
       <c r="W48" t="n">
-        <v>101693</v>
+        <v>293305</v>
       </c>
       <c r="X48" t="n">
-        <v>15037</v>
+        <v>43369</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>101693</v>
+        <v>293305</v>
       </c>
       <c r="AA48" t="n">
         <v>5</v>
@@ -6110,17 +6345,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Equipamentos</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6406,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -6188,34 +6428,34 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>48307</v>
+        <v>86656</v>
       </c>
       <c r="W49" t="n">
-        <v>48307</v>
+        <v>101693</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>15037</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>48307</v>
+        <v>101693</v>
       </c>
       <c r="AA49" t="n">
         <v>5</v>
@@ -6228,7 +6468,7 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>CPPSR - Equipamentos</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -6238,7 +6478,12 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6515,7 @@
         <v>4018</v>
       </c>
       <c r="G50" t="n">
-        <v>4321</v>
+        <v>2431</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6279,12 +6524,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -6306,34 +6551,34 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>16354</v>
+        <v>48307</v>
       </c>
       <c r="W50" t="n">
-        <v>20000</v>
+        <v>48307</v>
       </c>
       <c r="X50" t="n">
-        <v>3646</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>20000</v>
+        <v>48307</v>
       </c>
       <c r="AA50" t="n">
         <v>5</v>
@@ -6346,17 +6591,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Equipamentos</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6647,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6424,34 +6674,34 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5686750</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>5495750</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>10991500</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>5686750</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>5495750</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>18778855</v>
+        <v>16354</v>
       </c>
       <c r="W51" t="n">
-        <v>22965724</v>
+        <v>20000</v>
       </c>
       <c r="X51" t="n">
-        <v>4186869</v>
+        <v>3646</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>22965724</v>
+        <v>20000</v>
       </c>
       <c r="AA51" t="n">
         <v>5</v>
@@ -6464,17 +6714,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Políticas</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6506,16 +6761,16 @@
         <v>4018</v>
       </c>
       <c r="G52" t="n">
-        <v>9026</v>
+        <v>4321</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPPSR</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6542,34 +6797,34 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5686750</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>5495750</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>10991500</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>5686750</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>5495750</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>18778855</v>
       </c>
       <c r="W52" t="n">
-        <v>100000</v>
+        <v>22965724</v>
       </c>
       <c r="X52" t="n">
-        <v>100000</v>
+        <v>4186869</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>100000</v>
+        <v>22965724</v>
       </c>
       <c r="AA52" t="n">
         <v>5</v>
@@ -6577,22 +6832,27 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>População em Situação de Rua</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Políticas</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6884,7 @@
         <v>4018</v>
       </c>
       <c r="G53" t="n">
-        <v>9040</v>
+        <v>9026</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6678,16 +6938,16 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="X53" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="AA53" t="n">
         <v>5</v>
@@ -6700,7 +6960,7 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
@@ -6710,7 +6970,12 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6742,7 +7007,7 @@
         <v>4018</v>
       </c>
       <c r="G54" t="n">
-        <v>9041</v>
+        <v>9040</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6796,16 +7061,16 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="X54" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="Y54" t="n">
         <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="AA54" t="n">
         <v>5</v>
@@ -6818,7 +7083,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
@@ -6828,7 +7093,12 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6860,7 +7130,7 @@
         <v>4018</v>
       </c>
       <c r="G55" t="n">
-        <v>9042</v>
+        <v>9041</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6914,16 +7184,16 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="X55" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="AA55" t="n">
         <v>5</v>
@@ -6936,7 +7206,7 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
@@ -6946,7 +7216,12 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -6978,7 +7253,7 @@
         <v>4018</v>
       </c>
       <c r="G56" t="n">
-        <v>9043</v>
+        <v>9042</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -7032,16 +7307,16 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="X56" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="AA56" t="n">
         <v>5</v>
@@ -7054,7 +7329,7 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
@@ -7064,7 +7339,12 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7376,7 @@
         <v>4018</v>
       </c>
       <c r="G57" t="n">
-        <v>9045</v>
+        <v>9043</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -7172,7 +7452,7 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -7182,7 +7462,12 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7499,7 @@
         <v>4018</v>
       </c>
       <c r="G58" t="n">
-        <v>9046</v>
+        <v>9045</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -7268,16 +7553,16 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="X58" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="AA58" t="n">
         <v>5</v>
@@ -7290,7 +7575,7 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
@@ -7300,7 +7585,12 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7622,7 @@
         <v>4018</v>
       </c>
       <c r="G59" t="n">
-        <v>9051</v>
+        <v>9046</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -7386,16 +7676,16 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="X59" t="n">
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="AA59" t="n">
         <v>5</v>
@@ -7408,7 +7698,7 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -7418,7 +7708,12 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7745,7 @@
         <v>4018</v>
       </c>
       <c r="G60" t="n">
-        <v>9055</v>
+        <v>9051</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -7459,7 +7754,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7504,16 +7799,16 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="X60" t="n">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="AA60" t="n">
         <v>5</v>
@@ -7526,17 +7821,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7868,7 @@
         <v>4018</v>
       </c>
       <c r="G61" t="n">
-        <v>9097</v>
+        <v>9055</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -7577,7 +7877,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7622,16 +7922,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>2300000</v>
+        <v>200000</v>
       </c>
       <c r="X61" t="n">
-        <v>2300000</v>
+        <v>200000</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2300000</v>
+        <v>200000</v>
       </c>
       <c r="AA61" t="n">
         <v>5</v>
@@ -7644,17 +7944,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7683,19 +7988,19 @@
         <v>422</v>
       </c>
       <c r="F62" t="n">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="G62" t="n">
-        <v>4328</v>
+        <v>9097</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7722,34 +8027,34 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1226000</v>
+        <v>2300000</v>
       </c>
       <c r="X62" t="n">
-        <v>598343</v>
+        <v>2300000</v>
       </c>
       <c r="Y62" t="n">
         <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1226000</v>
+        <v>2300000</v>
       </c>
       <c r="AA62" t="n">
         <v>5</v>
@@ -7757,22 +8062,27 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7813,7 +8123,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7840,34 +8150,34 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>25389</v>
+        <v>627657</v>
       </c>
       <c r="W63" t="n">
-        <v>49592</v>
+        <v>1226000</v>
       </c>
       <c r="X63" t="n">
-        <v>24203</v>
+        <v>598343</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>49592</v>
+        <v>1226000</v>
       </c>
       <c r="AA63" t="n">
         <v>5</v>
@@ -7880,17 +8190,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -7931,7 +8246,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7958,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>868373</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -7967,25 +8282,25 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>868373</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>868373</v>
+        <v>25389</v>
       </c>
       <c r="W64" t="n">
-        <v>1696190</v>
+        <v>49592</v>
       </c>
       <c r="X64" t="n">
-        <v>827817</v>
+        <v>24203</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1696190</v>
+        <v>49592</v>
       </c>
       <c r="AA64" t="n">
         <v>5</v>
@@ -7998,17 +8313,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8369,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8058,7 +8378,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>122450</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -8067,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>122450</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8076,34 +8396,34 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>921519</v>
+        <v>868373</v>
       </c>
       <c r="R65" t="n">
-        <v>244900</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>244900</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>921519</v>
+        <v>868373</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>921519</v>
+        <v>868373</v>
       </c>
       <c r="W65" t="n">
-        <v>1800000</v>
+        <v>1696190</v>
       </c>
       <c r="X65" t="n">
-        <v>878481</v>
+        <v>827817</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1800000</v>
+        <v>1696190</v>
       </c>
       <c r="AA65" t="n">
         <v>5</v>
@@ -8116,17 +8436,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8155,19 +8480,19 @@
         <v>422</v>
       </c>
       <c r="F66" t="n">
-        <v>4023</v>
+        <v>4019</v>
       </c>
       <c r="G66" t="n">
-        <v>4320</v>
+        <v>4328</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CPPI</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8176,7 +8501,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>122450</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8185,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>122450</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8194,34 +8519,34 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>921519</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>244900</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>244900</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>921519</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>3000</v>
+        <v>921519</v>
       </c>
       <c r="W66" t="n">
-        <v>3000</v>
+        <v>1800000</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>878481</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>3000</v>
+        <v>1800000</v>
       </c>
       <c r="AA66" t="n">
         <v>5</v>
@@ -8229,22 +8554,27 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Idoso</t>
+          <t>Criança e Adolescente</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8606,7 @@
         <v>4023</v>
       </c>
       <c r="G67" t="n">
-        <v>4330</v>
+        <v>4320</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -8285,7 +8615,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8312,34 +8642,34 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1193451</v>
+        <v>3000</v>
       </c>
       <c r="W67" t="n">
-        <v>1671844</v>
+        <v>3000</v>
       </c>
       <c r="X67" t="n">
-        <v>478393</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1671844</v>
+        <v>3000</v>
       </c>
       <c r="AA67" t="n">
         <v>5</v>
@@ -8352,17 +8682,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Políticas</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8738,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8430,34 +8765,34 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>74955</v>
+        <v>1193451</v>
       </c>
       <c r="W68" t="n">
-        <v>105000</v>
+        <v>1671844</v>
       </c>
       <c r="X68" t="n">
-        <v>30045</v>
+        <v>478393</v>
       </c>
       <c r="Y68" t="n">
         <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>105000</v>
+        <v>1671844</v>
       </c>
       <c r="AA68" t="n">
         <v>5</v>
@@ -8470,17 +8805,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8861,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8563,19 +8903,19 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>616055</v>
+        <v>74955</v>
       </c>
       <c r="W69" t="n">
-        <v>863000</v>
+        <v>105000</v>
       </c>
       <c r="X69" t="n">
-        <v>246945</v>
+        <v>30045</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>863000</v>
+        <v>105000</v>
       </c>
       <c r="AA69" t="n">
         <v>5</v>
@@ -8588,17 +8928,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8984,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8666,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -8675,25 +9020,25 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>938683</v>
+        <v>616055</v>
       </c>
       <c r="W70" t="n">
-        <v>1314953</v>
+        <v>863000</v>
       </c>
       <c r="X70" t="n">
-        <v>376270</v>
+        <v>246945</v>
       </c>
       <c r="Y70" t="n">
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1314953</v>
+        <v>863000</v>
       </c>
       <c r="AA70" t="n">
         <v>5</v>
@@ -8706,17 +9051,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8762,7 +9112,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -8784,34 +9134,34 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>21270</v>
+        <v>55000</v>
       </c>
       <c r="R71" t="n">
-        <v>21270</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>21270</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>21270</v>
+        <v>55000</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>21270</v>
+        <v>938683</v>
       </c>
       <c r="W71" t="n">
-        <v>21270</v>
+        <v>1314953</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>376270</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>21270</v>
+        <v>1314953</v>
       </c>
       <c r="AA71" t="n">
         <v>5</v>
@@ -8824,7 +9174,7 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
@@ -8834,7 +9184,12 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8866,21 +9221,21 @@
         <v>4023</v>
       </c>
       <c r="G72" t="n">
-        <v>9028</v>
+        <v>4330</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPPI</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -8902,34 +9257,34 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="W72" t="n">
-        <v>100000</v>
+        <v>21270</v>
       </c>
       <c r="X72" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
         <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>100000</v>
+        <v>21270</v>
       </c>
       <c r="AA72" t="n">
         <v>5</v>
@@ -8937,22 +9292,27 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Idoso</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -8984,7 +9344,7 @@
         <v>4023</v>
       </c>
       <c r="G73" t="n">
-        <v>9038</v>
+        <v>9028</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -9060,7 +9420,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -9070,7 +9430,12 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9467,7 @@
         <v>4023</v>
       </c>
       <c r="G74" t="n">
-        <v>9050</v>
+        <v>9038</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -9156,16 +9521,16 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X74" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA74" t="n">
         <v>5</v>
@@ -9178,7 +9543,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -9188,7 +9553,12 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9217,14 +9587,14 @@
         <v>422</v>
       </c>
       <c r="F75" t="n">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="G75" t="n">
-        <v>2051</v>
+        <v>9050</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9256,34 +9626,34 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>1838981</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>2107032</v>
+        <v>75000</v>
       </c>
       <c r="X75" t="n">
-        <v>268051</v>
+        <v>75000</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>2107032</v>
+        <v>75000</v>
       </c>
       <c r="AA75" t="n">
         <v>5</v>
@@ -9291,12 +9661,12 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
@@ -9306,7 +9676,12 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9722,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9374,34 +9749,34 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>69823</v>
+        <v>1838981</v>
       </c>
       <c r="W76" t="n">
-        <v>80000</v>
+        <v>2107032</v>
       </c>
       <c r="X76" t="n">
-        <v>10177</v>
+        <v>268051</v>
       </c>
       <c r="Y76" t="n">
         <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>80000</v>
+        <v>2107032</v>
       </c>
       <c r="AA76" t="n">
         <v>5</v>
@@ -9414,17 +9789,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9845,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9507,19 +9887,19 @@
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>130917</v>
+        <v>69823</v>
       </c>
       <c r="W77" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="X77" t="n">
-        <v>19083</v>
+        <v>10177</v>
       </c>
       <c r="Y77" t="n">
         <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="AA77" t="n">
         <v>5</v>
@@ -9532,17 +9912,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9968,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9610,7 +9995,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -9619,25 +10004,25 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>392752</v>
+        <v>130917</v>
       </c>
       <c r="W78" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="X78" t="n">
-        <v>57248</v>
+        <v>19083</v>
       </c>
       <c r="Y78" t="n">
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="AA78" t="n">
         <v>5</v>
@@ -9650,17 +10035,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9692,16 +10082,16 @@
         <v>4024</v>
       </c>
       <c r="G79" t="n">
-        <v>2142</v>
+        <v>2051</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>EDH</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9725,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>49471</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9737,25 +10127,25 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>50000</v>
+        <v>392752</v>
       </c>
       <c r="W79" t="n">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="X79" t="n">
-        <v>49471</v>
+        <v>57248</v>
       </c>
       <c r="Y79" t="n">
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="AA79" t="n">
         <v>5</v>
@@ -9763,22 +10153,27 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Educação em Direitos Humanos</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9819,7 +10214,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9843,7 +10238,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>49471</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -9861,19 +10256,19 @@
         <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>1058</v>
+        <v>50000</v>
       </c>
       <c r="W80" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="X80" t="n">
-        <v>98942</v>
+        <v>49471</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="AA80" t="n">
         <v>5</v>
@@ -9886,17 +10281,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -9937,7 +10337,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9961,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>49471</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -9979,19 +10379,19 @@
         <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>50000</v>
+        <v>1058</v>
       </c>
       <c r="W81" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="X81" t="n">
-        <v>49471</v>
+        <v>98942</v>
       </c>
       <c r="Y81" t="n">
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="AA81" t="n">
         <v>5</v>
@@ -10004,17 +10404,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10460,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10079,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>49471</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -10097,19 +10502,19 @@
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>13341</v>
+        <v>50000</v>
       </c>
       <c r="W82" t="n">
-        <v>1261000</v>
+        <v>50000</v>
       </c>
       <c r="X82" t="n">
-        <v>1247659</v>
+        <v>49471</v>
       </c>
       <c r="Y82" t="n">
         <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1261000</v>
+        <v>50000</v>
       </c>
       <c r="AA82" t="n">
         <v>5</v>
@@ -10122,17 +10527,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10164,16 +10574,16 @@
         <v>4024</v>
       </c>
       <c r="G83" t="n">
-        <v>3406</v>
+        <v>2142</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Selo DH</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>44903900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10215,19 +10625,19 @@
         <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1000</v>
+        <v>13341</v>
       </c>
       <c r="W83" t="n">
-        <v>1000</v>
+        <v>1261000</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1247659</v>
       </c>
       <c r="Y83" t="n">
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1000</v>
+        <v>1261000</v>
       </c>
       <c r="AA83" t="n">
         <v>5</v>
@@ -10235,22 +10645,27 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Selo DH</t>
+          <t>Educação em Direitos Humanos</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10282,16 +10697,16 @@
         <v>4024</v>
       </c>
       <c r="G84" t="n">
-        <v>4314</v>
+        <v>3406</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Desaparecidas</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44903900</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10333,19 +10748,19 @@
         <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W84" t="n">
-        <v>550500</v>
+        <v>1000</v>
       </c>
       <c r="X84" t="n">
-        <v>550500</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>550500</v>
+        <v>1000</v>
       </c>
       <c r="AA84" t="n">
         <v>5</v>
@@ -10353,22 +10768,27 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Desaparecidos</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Material Permanente</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10400,16 +10820,16 @@
         <v>4024</v>
       </c>
       <c r="G85" t="n">
-        <v>4317</v>
+        <v>4314</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DMV</t>
+          <t>Desaparecidas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10451,19 +10871,19 @@
         <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1000</v>
+        <v>550500</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>550500</v>
       </c>
       <c r="Y85" t="n">
         <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1000</v>
+        <v>550500</v>
       </c>
       <c r="AA85" t="n">
         <v>5</v>
@@ -10471,22 +10891,27 @@
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Memória e Verdade</t>
+          <t>Desaparecidos</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Desaparecidas</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10518,16 +10943,16 @@
         <v>4024</v>
       </c>
       <c r="G86" t="n">
-        <v>4318</v>
+        <v>4317</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>DMV</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10554,25 +10979,25 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>12675633</v>
+        <v>1000</v>
       </c>
       <c r="W86" t="n">
-        <v>12675633</v>
+        <v>1000</v>
       </c>
       <c r="X86" t="n">
         <v>0</v>
@@ -10581,7 +11006,7 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>12675633</v>
+        <v>1000</v>
       </c>
       <c r="AA86" t="n">
         <v>5</v>
@@ -10589,22 +11014,27 @@
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Memória e Verdade</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>DMV</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10645,7 +11075,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10672,25 +11102,25 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="W87" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
@@ -10699,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="AA87" t="n">
         <v>5</v>
@@ -10712,17 +11142,22 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10763,7 +11198,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10805,10 +11240,10 @@
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="W88" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
@@ -10817,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="AA88" t="n">
         <v>5</v>
@@ -10830,17 +11265,22 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10872,16 +11312,16 @@
         <v>4024</v>
       </c>
       <c r="G89" t="n">
-        <v>4319</v>
+        <v>4318</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10923,19 +11363,19 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>8373</v>
+        <v>378632</v>
       </c>
       <c r="W89" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="X89" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="AA89" t="n">
         <v>5</v>
@@ -10943,22 +11383,27 @@
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -10999,12 +11444,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -11041,19 +11486,19 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>4000</v>
+        <v>8373</v>
       </c>
       <c r="W90" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="AA90" t="n">
         <v>5</v>
@@ -11066,17 +11511,22 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11117,12 +11567,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -11144,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -11153,25 +11603,25 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>9813947</v>
+        <v>4000</v>
       </c>
       <c r="W91" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="X91" t="n">
-        <v>2607835</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="AA91" t="n">
         <v>5</v>
@@ -11184,17 +11634,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Código Genérico</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11226,16 +11681,16 @@
         <v>4024</v>
       </c>
       <c r="G92" t="n">
-        <v>4324</v>
+        <v>4319</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11262,7 +11717,7 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -11271,25 +11726,25 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="W92" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="X92" t="n">
-        <v>56000</v>
+        <v>2607835</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="AA92" t="n">
         <v>5</v>
@@ -11297,22 +11752,27 @@
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11818,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -11398,16 +11858,16 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Y93" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AA93" t="n">
         <v>5</v>
@@ -11420,7 +11880,7 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -11430,7 +11890,12 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11941,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -11486,7 +11951,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -11513,19 +11978,19 @@
         <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="X94" t="n">
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Z94" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>5</v>
@@ -11538,7 +12003,7 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -11548,7 +12013,12 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11594,7 +12064,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -11656,7 +12126,7 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
@@ -11666,7 +12136,12 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11712,7 +12187,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -11722,7 +12197,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -11749,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
@@ -11761,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AA96" t="n">
         <v>5</v>
@@ -11774,7 +12249,7 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -11784,7 +12259,12 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11816,11 +12296,11 @@
         <v>4024</v>
       </c>
       <c r="G97" t="n">
-        <v>4325</v>
+        <v>4324</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11830,7 +12310,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -11840,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -11867,10 +12347,10 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W97" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
         <v>0</v>
@@ -11879,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AA97" t="n">
         <v>5</v>
@@ -11887,12 +12367,12 @@
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
@@ -11902,7 +12382,12 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -11934,16 +12419,16 @@
         <v>4024</v>
       </c>
       <c r="G98" t="n">
-        <v>4326</v>
+        <v>4325</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11970,25 +12455,25 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="W98" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="X98" t="n">
         <v>0</v>
@@ -11997,7 +12482,7 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="AA98" t="n">
         <v>5</v>
@@ -12005,22 +12490,27 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12551,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12088,25 +12578,25 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="W99" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
@@ -12115,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="AA99" t="n">
         <v>5</v>
@@ -12128,17 +12618,22 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12674,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12206,7 +12701,7 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -12215,16 +12710,16 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="W100" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
@@ -12233,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="AA100" t="n">
         <v>5</v>
@@ -12246,17 +12741,22 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12288,16 +12788,16 @@
         <v>4024</v>
       </c>
       <c r="G101" t="n">
-        <v>4332</v>
+        <v>4326</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12324,25 +12824,25 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>5238691</v>
+        <v>6926170.67</v>
       </c>
       <c r="R101" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>8823589.4</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>5238691</v>
+        <v>6926170.67</v>
       </c>
       <c r="U101" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="W101" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -12351,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="AA101" t="n">
         <v>5</v>
@@ -12359,22 +12859,27 @@
       <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12920,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12442,25 +12947,25 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>5238691</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>8823589.4</v>
       </c>
       <c r="T102" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="V102" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="W102" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="X102" t="n">
         <v>0</v>
@@ -12469,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="AA102" t="n">
         <v>5</v>
@@ -12482,17 +12987,22 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12524,16 +13034,16 @@
         <v>4024</v>
       </c>
       <c r="G103" t="n">
-        <v>4333</v>
+        <v>4332</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12560,7 +13070,7 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -12569,16 +13079,16 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="W103" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
@@ -12587,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="AA103" t="n">
         <v>5</v>
@@ -12595,22 +13105,27 @@
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12651,7 +13166,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12678,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -12687,16 +13202,16 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="W104" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
@@ -12705,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="AA104" t="n">
         <v>5</v>
@@ -12718,17 +13233,22 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12774,7 +13294,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -12790,31 +13310,31 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>46120</v>
+        <v>13728.92</v>
       </c>
       <c r="R105" t="n">
-        <v>43870</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>45670</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>44320</v>
+        <v>13728.92</v>
       </c>
       <c r="U105" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="W105" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -12823,7 +13343,7 @@
         <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="AA105" t="n">
         <v>5</v>
@@ -12836,7 +13356,7 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
@@ -12846,7 +13366,12 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12878,21 +13403,21 @@
         <v>4024</v>
       </c>
       <c r="G106" t="n">
-        <v>4335</v>
+        <v>4333</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -12908,31 +13433,31 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>46120</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>43870</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>44320</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="V106" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="W106" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
@@ -12941,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="AA106" t="n">
         <v>5</v>
@@ -12949,22 +13474,27 @@
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -12993,14 +13523,14 @@
         <v>422</v>
       </c>
       <c r="F107" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G107" t="n">
-        <v>2053</v>
+        <v>4335</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -13014,7 +13544,7 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -13023,7 +13553,7 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13032,34 +13562,34 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>4887292</v>
+        <v>50000</v>
       </c>
       <c r="W107" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="X107" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="AA107" t="n">
         <v>5</v>
@@ -13067,12 +13597,12 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
@@ -13082,7 +13612,12 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13128,11 +13663,11 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -13141,7 +13676,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13150,34 +13685,34 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="W108" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="X108" t="n">
-        <v>2000</v>
+        <v>261863</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="AA108" t="n">
         <v>5</v>
@@ -13190,7 +13725,7 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -13200,7 +13735,12 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13241,12 +13781,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -13268,34 +13808,34 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>150755</v>
+        <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="X109" t="n">
-        <v>8077</v>
+        <v>2000</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="AA109" t="n">
         <v>5</v>
@@ -13308,17 +13848,22 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Código Genérico</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13904,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13386,34 +13931,34 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>519437</v>
+        <v>150755</v>
       </c>
       <c r="W110" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="X110" t="n">
-        <v>27832</v>
+        <v>8077</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="AA110" t="n">
         <v>5</v>
@@ -13426,17 +13971,22 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13477,7 +14027,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13498,40 +14048,40 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>2664</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>139083</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>4701261</v>
+        <v>519437</v>
       </c>
       <c r="W111" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="X111" t="n">
-        <v>251895</v>
+        <v>27832</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="AA111" t="n">
         <v>5</v>
@@ -13544,17 +14094,22 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13600,7 +14155,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -13616,40 +14171,40 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>2664</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>282533</v>
+        <v>139083</v>
       </c>
       <c r="R112" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="S112" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="T112" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>282533</v>
+        <v>4701261</v>
       </c>
       <c r="W112" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>251895</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="AA112" t="n">
         <v>5</v>
@@ -13662,7 +14217,7 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
@@ -13672,7 +14227,12 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13713,12 +14273,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -13740,34 +14300,34 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="W113" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="X113" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="AA113" t="n">
         <v>5</v>
@@ -13780,17 +14340,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13822,7 +14387,7 @@
         <v>4025</v>
       </c>
       <c r="G114" t="n">
-        <v>4329</v>
+        <v>2053</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -13831,7 +14396,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13840,7 +14405,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -13849,7 +14414,7 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -13858,34 +14423,34 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>2356400</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="X114" t="n">
-        <v>1421600</v>
+        <v>10000</v>
       </c>
       <c r="Y114" t="n">
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="AA114" t="n">
         <v>5</v>
@@ -13898,17 +14463,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -13940,7 +14510,7 @@
         <v>4025</v>
       </c>
       <c r="G115" t="n">
-        <v>6178</v>
+        <v>4329</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -13949,7 +14519,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13958,7 +14528,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -13967,43 +14537,43 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="O115" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="R115" t="n">
-        <v>21164757.5</v>
+        <v>1576800</v>
       </c>
       <c r="S115" t="n">
-        <v>21344367.15</v>
+        <v>2356400</v>
       </c>
       <c r="T115" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="U115" t="n">
-        <v>179609.65</v>
+        <v>779600</v>
       </c>
       <c r="V115" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="W115" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Y115" t="n">
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="AA115" t="n">
         <v>5</v>
@@ -14016,17 +14586,22 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14642,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -14088,31 +14663,31 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>106229.82</v>
+        <v>23851875.51</v>
       </c>
       <c r="R116" t="n">
-        <v>16178</v>
+        <v>21164757.5</v>
       </c>
       <c r="S116" t="n">
-        <v>17972</v>
+        <v>21344367.15</v>
       </c>
       <c r="T116" t="n">
-        <v>106229.82</v>
+        <v>22426358</v>
       </c>
       <c r="U116" t="n">
-        <v>1794</v>
+        <v>179609.65</v>
       </c>
       <c r="V116" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="W116" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -14121,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AA116" t="n">
         <v>5</v>
@@ -14134,17 +14709,22 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14765,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14212,25 +14792,25 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>88531.96000000001</v>
+        <v>106229.82</v>
       </c>
       <c r="R117" t="n">
-        <v>88531.96000000001</v>
+        <v>16178</v>
       </c>
       <c r="S117" t="n">
-        <v>88531.96000000001</v>
+        <v>17972</v>
       </c>
       <c r="T117" t="n">
-        <v>88531.96000000001</v>
+        <v>106229.82</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="V117" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="W117" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -14239,7 +14819,7 @@
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AA117" t="n">
         <v>5</v>
@@ -14252,17 +14832,22 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14888,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14330,25 +14915,25 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>306807.5</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="T118" t="n">
-        <v>306807.5</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="W118" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -14357,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AA118" t="n">
         <v>5</v>
@@ -14370,17 +14955,22 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14421,7 +15011,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -14448,7 +15038,7 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>988754.48</v>
+        <v>306807.5</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -14457,16 +15047,16 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>988754.48</v>
+        <v>306807.5</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="W119" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -14475,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AA119" t="n">
         <v>5</v>
@@ -14488,17 +15078,22 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14544,7 +15139,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -14566,25 +15161,25 @@
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>80000</v>
+        <v>988754.48</v>
       </c>
       <c r="R120" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>80000</v>
+        <v>988754.48</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="W120" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -14593,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AA120" t="n">
         <v>5</v>
@@ -14606,7 +15201,7 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -14616,7 +15211,12 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14657,12 +15257,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -14684,25 +15284,25 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="R121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="S121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="T121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="W121" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -14711,7 +15311,7 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AA121" t="n">
         <v>5</v>
@@ -14724,17 +15324,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14766,16 +15371,16 @@
         <v>4025</v>
       </c>
       <c r="G122" t="n">
-        <v>9027</v>
+        <v>6178</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14802,34 +15407,34 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="W122" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X122" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AA122" t="n">
         <v>5</v>
@@ -14837,22 +15442,27 @@
       <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -14884,7 +15494,7 @@
         <v>4025</v>
       </c>
       <c r="G123" t="n">
-        <v>9030</v>
+        <v>9027</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -14938,16 +15548,16 @@
         <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="X123" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AA123" t="n">
         <v>5</v>
@@ -14960,7 +15570,7 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
@@ -14970,7 +15580,12 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15617,7 @@
         <v>4025</v>
       </c>
       <c r="G124" t="n">
-        <v>9044</v>
+        <v>9030</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -15056,16 +15671,16 @@
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X124" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA124" t="n">
         <v>5</v>
@@ -15078,7 +15693,7 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
@@ -15088,7 +15703,12 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15117,19 +15737,19 @@
         <v>422</v>
       </c>
       <c r="F125" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G125" t="n">
-        <v>4327</v>
+        <v>9044</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -15171,19 +15791,19 @@
         <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="AA125" t="n">
         <v>5</v>
@@ -15191,22 +15811,27 @@
       <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15238,7 +15863,7 @@
         <v>4026</v>
       </c>
       <c r="G126" t="n">
-        <v>4334</v>
+        <v>4327</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -15247,7 +15872,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15274,34 +15899,34 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>3469273</v>
+        <v>11949</v>
       </c>
       <c r="W126" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="X126" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AA126" t="n">
         <v>5</v>
@@ -15314,17 +15939,22 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15995,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15392,34 +16022,34 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>5374</v>
+        <v>3469273</v>
       </c>
       <c r="W127" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="X127" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AA127" t="n">
         <v>5</v>
@@ -15432,17 +16062,22 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15483,7 +16118,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15525,19 +16160,19 @@
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="W128" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="X128" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AA128" t="n">
         <v>5</v>
@@ -15550,17 +16185,22 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15601,7 +16241,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15628,7 +16268,7 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -15637,25 +16277,25 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="W129" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="X129" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AA129" t="n">
         <v>5</v>
@@ -15668,17 +16308,22 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15724,7 +16369,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -15746,7 +16391,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>225</v>
+        <v>4890595.9</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -15755,25 +16400,25 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>225</v>
+        <v>4890595.9</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="W130" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AA130" t="n">
         <v>5</v>
@@ -15786,7 +16431,7 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
@@ -15796,7 +16441,12 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15828,21 +16478,21 @@
         <v>4026</v>
       </c>
       <c r="G131" t="n">
-        <v>9025</v>
+        <v>4334</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -15864,7 +16514,7 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -15873,25 +16523,25 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W131" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="X131" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="AA131" t="n">
         <v>5</v>
@@ -15899,22 +16549,27 @@
       <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -15940,22 +16595,22 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F132" t="n">
         <v>4026</v>
       </c>
       <c r="G132" t="n">
-        <v>4322</v>
+        <v>9025</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15997,19 +16652,19 @@
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>7143</v>
+        <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="X132" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Y132" t="n">
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="AA132" t="n">
         <v>5</v>
@@ -16017,22 +16672,27 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16733,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16100,7 +16760,7 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -16109,25 +16769,25 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>33669</v>
+        <v>7143</v>
       </c>
       <c r="W133" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="X133" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AA133" t="n">
         <v>5</v>
@@ -16140,17 +16800,22 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -16182,16 +16847,16 @@
         <v>4026</v>
       </c>
       <c r="G134" t="n">
-        <v>9234</v>
+        <v>4322</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -16218,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -16227,25 +16892,25 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="W134" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="X134" t="n">
-        <v>100000</v>
+        <v>187297</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="AA134" t="n">
         <v>5</v>
@@ -16253,22 +16918,27 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -16280,12 +16950,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16294,22 +16964,22 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F135" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G135" t="n">
-        <v>4426</v>
+        <v>9234</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16354,16 +17024,16 @@
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="X135" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="AA135" t="n">
         <v>5</v>
@@ -16371,63 +17041,68 @@
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F136" t="n">
         <v>4010</v>
       </c>
       <c r="G136" t="n">
-        <v>4302</v>
+        <v>4426</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -16436,7 +17111,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>3235052.09</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -16454,34 +17129,34 @@
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AA136" t="n">
         <v>5</v>
@@ -16494,17 +17169,22 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -16545,7 +17225,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16554,7 +17234,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>3235052.09</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -16563,7 +17243,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3235052.09</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16572,34 +17252,34 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="W137" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="X137" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AA137" t="n">
         <v>5</v>
@@ -16612,17 +17292,22 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -16644,21 +17329,21 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F138" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G138" t="n">
-        <v>3002</v>
+        <v>4302</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -16705,19 +17390,19 @@
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="W138" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AA138" t="n">
         <v>5</v>
@@ -16730,7 +17415,7 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE138" t="inlineStr">
@@ -16740,7 +17425,12 @@
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -16766,13 +17456,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F139" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G139" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -16781,7 +17471,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16790,7 +17480,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>438463.7</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -16802,40 +17492,40 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>16556247.06</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>133336049.87</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>103758007.13</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>106566937.33</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>116779802.81</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>2808930.2</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>166077092</v>
+        <v>1000</v>
       </c>
       <c r="W139" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="X139" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="AA139" t="n">
         <v>5</v>
@@ -16848,17 +17538,22 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -16899,16 +17594,16 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>438463.7</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -16920,40 +17615,40 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>16556247.06</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>133336049.87</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>103758007.13</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>106566937.33</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>116779802.81</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
+        <v>2808930.2</v>
       </c>
       <c r="V140" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="W140" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="X140" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AA140" t="n">
         <v>5</v>
@@ -16966,17 +17661,22 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17722,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -17059,10 +17759,10 @@
         <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="W141" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X141" t="n">
         <v>0</v>
@@ -17071,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AA141" t="n">
         <v>5</v>
@@ -17084,7 +17784,7 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic. de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
@@ -17094,7 +17794,12 @@
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17135,16 +17840,16 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -17156,40 +17861,40 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>52634438.4</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="W142" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="X142" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AA142" t="n">
         <v>5</v>
@@ -17202,17 +17907,22 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17963,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -17262,7 +17972,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>5410565.4</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -17274,40 +17984,40 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>180000</v>
+        <v>26317219.2</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>31750960.63</v>
+        <v>52634438.4</v>
       </c>
       <c r="R143" t="n">
-        <v>31570960.63</v>
+        <v>26317219.2</v>
       </c>
       <c r="S143" t="n">
-        <v>31570960.63</v>
+        <v>26317219.2</v>
       </c>
       <c r="T143" t="n">
-        <v>31570960.63</v>
+        <v>26317219.2</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>80849746</v>
+        <v>136889022</v>
       </c>
       <c r="W143" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="X143" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Y143" t="n">
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="AA143" t="n">
         <v>5</v>
@@ -17320,17 +18030,22 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17376,7 +18091,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K144" t="n">
@@ -17392,40 +18107,40 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>31750960.63</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>31570960.63</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>31570960.63</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>31570960.63</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>2000</v>
+        <v>80849746</v>
       </c>
       <c r="W144" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="AA144" t="n">
         <v>5</v>
@@ -17438,7 +18153,7 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr">
@@ -17448,19 +18163,24 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -17474,27 +18194,27 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F145" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G145" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -17531,10 +18251,10 @@
         <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="W145" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="X145" t="n">
         <v>0</v>
@@ -17543,7 +18263,7 @@
         <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AA145" t="n">
         <v>5</v>
@@ -17551,22 +18271,27 @@
       <c r="AB145" t="inlineStr"/>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17607,7 +18332,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17649,10 +18374,10 @@
         <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="W146" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -17661,7 +18386,7 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AA146" t="n">
         <v>5</v>
@@ -17674,17 +18399,22 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17710,22 +18440,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F147" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G147" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17767,10 +18497,10 @@
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="W147" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -17779,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -17787,22 +18517,27 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17828,27 +18563,27 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F148" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G148" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -17885,10 +18620,10 @@
         <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W148" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -17897,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA148" t="n">
         <v>5</v>
@@ -17905,22 +18640,27 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serv. de Tec. da Inf. e Com - PJ</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>31/01/2026 08:28:52</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>
@@ -17966,11 +18706,11 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>1433738.57</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -17982,31 +18722,31 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>35187195.47</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>31855789.6</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>33468553.7</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>32118763.49</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -18015,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AA149" t="n">
         <v>5</v>
@@ -18028,17 +18768,145 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>422</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G150" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>1433738.57</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>127680</v>
+      </c>
+      <c r="O150" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>35187195.47</v>
+      </c>
+      <c r="R150" t="n">
+        <v>31855789.6</v>
+      </c>
+      <c r="S150" t="n">
+        <v>33468553.7</v>
+      </c>
+      <c r="T150" t="n">
+        <v>32118763.49</v>
+      </c>
+      <c r="U150" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="V150" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="W150" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>31/01/2026 08:28:52</t>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>04/02/2026 15:36:37</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202601.xlsx
+++ b/base_despesas/2026/despesas_202601.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG150"/>
+  <dimension ref="A1:AG152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>50000</v>
+        <v>84200</v>
       </c>
       <c r="W4" t="n">
         <v>50000</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>50000</v>
+        <v>84200</v>
       </c>
       <c r="AA4" t="n">
         <v>5</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC - Manutenção</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação - PJ</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Tecnologia - Comunicação</t>
+          <t>DTIC - Comunicação</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Tecnologia - Comunicação</t>
+          <t>DTIC - Comunicação</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação - PJ</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Tecnologia - Comunicação</t>
+          <t>DTIC - Comunicação</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação - PJ</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>Planejamento e Informação</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>16294924</v>
+        <v>16260724</v>
       </c>
       <c r="W43" t="n">
         <v>21072104</v>
@@ -5714,10 +5714,10 @@
         <v>4777180</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="Z43" t="n">
-        <v>21072104</v>
+        <v>21037904</v>
       </c>
       <c r="AA43" t="n">
         <v>5</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10768,14 +10768,14 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
+          <t>Selo Direitos Humanos</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
           <t>Selo DH</t>
         </is>
       </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>Selo DH</t>
-        </is>
-      </c>
       <c r="AE84" t="inlineStr">
         <is>
           <t>Material Permanente</t>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Desaparecidas</t>
+          <t>CLFD</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Desaparecidas</t>
+          <t>CLFD - Políticas</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Memória e Verdade</t>
+          <t>Direito à Memória e Verdade</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -11102,25 +11102,25 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
@@ -11129,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>5</v>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Ricardo Teixeira</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11225,25 +11225,25 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="W88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="AA88" t="n">
         <v>5</v>
@@ -11265,12 +11265,12 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11363,10 +11363,10 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="W89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="AA89" t="n">
         <v>5</v>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11435,16 +11435,16 @@
         <v>4024</v>
       </c>
       <c r="G90" t="n">
-        <v>4319</v>
+        <v>4318</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11486,19 +11486,19 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>8373</v>
+        <v>378632</v>
       </c>
       <c r="W90" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="X90" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="AA90" t="n">
         <v>5</v>
@@ -11506,17 +11506,17 @@
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>CPLGBTI - Políticas</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11567,12 +11567,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -11609,19 +11609,19 @@
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>4000</v>
+        <v>8373</v>
       </c>
       <c r="W91" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="AA91" t="n">
         <v>5</v>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -11717,7 +11717,7 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -11726,25 +11726,25 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>9813947</v>
+        <v>4000</v>
       </c>
       <c r="W92" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="X92" t="n">
-        <v>2607835</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="AA92" t="n">
         <v>5</v>
@@ -11762,17 +11762,17 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11804,16 +11804,16 @@
         <v>4024</v>
       </c>
       <c r="G93" t="n">
-        <v>4324</v>
+        <v>4319</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11840,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -11849,25 +11849,25 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="W93" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="X93" t="n">
-        <v>56000</v>
+        <v>2607835</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="AA93" t="n">
         <v>5</v>
@@ -11875,17 +11875,17 @@
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>CPIPTD - Políticas</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -11981,16 +11981,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Y94" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AA94" t="n">
         <v>5</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -12101,19 +12101,19 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Z95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>5</v>
@@ -12136,12 +12136,12 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -12320,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -12359,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AA97" t="n">
         <v>5</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12419,11 +12419,11 @@
         <v>4024</v>
       </c>
       <c r="G98" t="n">
-        <v>4325</v>
+        <v>4324</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -12443,7 +12443,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W98" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
         <v>0</v>
@@ -12482,7 +12482,7 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AA98" t="n">
         <v>5</v>
@@ -12490,12 +12490,12 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -12505,12 +12505,12 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12542,16 +12542,16 @@
         <v>4024</v>
       </c>
       <c r="G99" t="n">
-        <v>4326</v>
+        <v>4325</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12578,25 +12578,25 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="W99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
@@ -12605,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="AA99" t="n">
         <v>5</v>
@@ -12613,17 +12613,17 @@
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>CPLGBTI - Equipamentos</t>
+          <t>CPD - Políticas</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12701,25 +12701,25 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="W100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
@@ -12728,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="AA100" t="n">
         <v>5</v>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12824,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -12833,16 +12833,16 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="W101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -12851,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="AA101" t="n">
         <v>5</v>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -12911,16 +12911,16 @@
         <v>4024</v>
       </c>
       <c r="G102" t="n">
-        <v>4332</v>
+        <v>4326</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12947,25 +12947,25 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>5238691</v>
+        <v>6926170.67</v>
       </c>
       <c r="R102" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>8823589.4</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>5238691</v>
+        <v>6926170.67</v>
       </c>
       <c r="U102" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="W102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="X102" t="n">
         <v>0</v>
@@ -12974,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="AA102" t="n">
         <v>5</v>
@@ -12982,17 +12982,17 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13070,25 +13070,25 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>5238691</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>8823589.4</v>
       </c>
       <c r="T103" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="V103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="W103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="AA103" t="n">
         <v>5</v>
@@ -13110,12 +13110,12 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13157,16 +13157,16 @@
         <v>4024</v>
       </c>
       <c r="G104" t="n">
-        <v>4333</v>
+        <v>4332</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13193,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -13202,16 +13202,16 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="W104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
@@ -13220,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="AA104" t="n">
         <v>5</v>
@@ -13228,17 +13228,17 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13316,7 +13316,7 @@
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -13325,16 +13325,16 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="W105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -13343,7 +13343,7 @@
         <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="AA105" t="n">
         <v>5</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -13433,31 +13433,31 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>46120</v>
+        <v>13728.92</v>
       </c>
       <c r="R106" t="n">
-        <v>43870</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>45670</v>
+        <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>44320</v>
+        <v>13728.92</v>
       </c>
       <c r="U106" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="W106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
@@ -13466,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="AA106" t="n">
         <v>5</v>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13526,21 +13526,21 @@
         <v>4024</v>
       </c>
       <c r="G107" t="n">
-        <v>4335</v>
+        <v>4333</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -13556,31 +13556,31 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>46120</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>43870</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>44320</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="V107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="W107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="AA107" t="n">
         <v>5</v>
@@ -13597,27 +13597,27 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13646,14 +13646,14 @@
         <v>422</v>
       </c>
       <c r="F108" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G108" t="n">
-        <v>2053</v>
+        <v>4335</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPEF</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -13676,7 +13676,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13685,34 +13685,34 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>4887292</v>
+        <v>50000</v>
       </c>
       <c r="W108" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="X108" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="AA108" t="n">
         <v>5</v>
@@ -13720,12 +13720,12 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos e Familiares</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPEF - Políticas</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13786,11 +13786,11 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13808,34 +13808,34 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="W109" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="X109" t="n">
-        <v>2000</v>
+        <v>261863</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="AA109" t="n">
         <v>5</v>
@@ -13848,7 +13848,7 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
@@ -13858,12 +13858,12 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -13904,12 +13904,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -13931,34 +13931,34 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>150755</v>
+        <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="X110" t="n">
-        <v>8077</v>
+        <v>2000</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="AA110" t="n">
         <v>5</v>
@@ -13971,22 +13971,22 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14054,34 +14054,34 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>519437</v>
+        <v>150755</v>
       </c>
       <c r="W111" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="X111" t="n">
-        <v>27832</v>
+        <v>8077</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="AA111" t="n">
         <v>5</v>
@@ -14094,12 +14094,12 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -14171,40 +14171,40 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>2664</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>139083</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>4701261</v>
+        <v>519437</v>
       </c>
       <c r="W112" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="X112" t="n">
-        <v>251895</v>
+        <v>27832</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="AA112" t="n">
         <v>5</v>
@@ -14217,12 +14217,12 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14278,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -14294,40 +14294,40 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>2664</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>282533</v>
+        <v>139083</v>
       </c>
       <c r="R113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="S113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="T113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>282533</v>
+        <v>4701261</v>
       </c>
       <c r="W113" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>251895</v>
       </c>
       <c r="Y113" t="n">
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="AA113" t="n">
         <v>5</v>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
@@ -14350,12 +14350,12 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14396,12 +14396,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -14423,34 +14423,34 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="W114" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="X114" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="AA114" t="n">
         <v>5</v>
@@ -14463,22 +14463,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
         <v>4025</v>
       </c>
       <c r="G115" t="n">
-        <v>4329</v>
+        <v>2053</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14546,34 +14546,34 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>2356400</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="V115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="X115" t="n">
-        <v>1421600</v>
+        <v>10000</v>
       </c>
       <c r="Y115" t="n">
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="AA115" t="n">
         <v>5</v>
@@ -14586,12 +14586,12 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
         <v>4025</v>
       </c>
       <c r="G116" t="n">
-        <v>6178</v>
+        <v>4329</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -14660,43 +14660,43 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="O116" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="R116" t="n">
-        <v>21164757.5</v>
+        <v>1576800</v>
       </c>
       <c r="S116" t="n">
-        <v>21344367.15</v>
+        <v>2356400</v>
       </c>
       <c r="T116" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="U116" t="n">
-        <v>179609.65</v>
+        <v>779600</v>
       </c>
       <c r="V116" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="W116" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Y116" t="n">
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="AA116" t="n">
         <v>5</v>
@@ -14709,12 +14709,12 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14786,31 +14786,31 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>106229.82</v>
+        <v>23851875.51</v>
       </c>
       <c r="R117" t="n">
-        <v>16178</v>
+        <v>21164757.5</v>
       </c>
       <c r="S117" t="n">
-        <v>17972</v>
+        <v>21344367.15</v>
       </c>
       <c r="T117" t="n">
-        <v>106229.82</v>
+        <v>22426358</v>
       </c>
       <c r="U117" t="n">
-        <v>1794</v>
+        <v>179609.65</v>
       </c>
       <c r="V117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="W117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -14819,7 +14819,7 @@
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AA117" t="n">
         <v>5</v>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14915,25 +14915,25 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>88531.96000000001</v>
+        <v>106229.82</v>
       </c>
       <c r="R118" t="n">
-        <v>88531.96000000001</v>
+        <v>16178</v>
       </c>
       <c r="S118" t="n">
-        <v>88531.96000000001</v>
+        <v>17972</v>
       </c>
       <c r="T118" t="n">
-        <v>88531.96000000001</v>
+        <v>106229.82</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="V118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="W118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -14942,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AA118" t="n">
         <v>5</v>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15038,25 +15038,25 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>306807.5</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="T119" t="n">
-        <v>306807.5</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="W119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AA119" t="n">
         <v>5</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -15161,7 +15161,7 @@
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>988754.48</v>
+        <v>306807.5</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
@@ -15170,16 +15170,16 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>988754.48</v>
+        <v>306807.5</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="W120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AA120" t="n">
         <v>5</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -15284,25 +15284,25 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>80000</v>
+        <v>988754.48</v>
       </c>
       <c r="R121" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>80000</v>
+        <v>988754.48</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="W121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AA121" t="n">
         <v>5</v>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15380,12 +15380,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -15407,25 +15407,25 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="R122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="S122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="T122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="W122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X122" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AA122" t="n">
         <v>5</v>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15494,16 +15494,16 @@
         <v>4025</v>
       </c>
       <c r="G123" t="n">
-        <v>9027</v>
+        <v>6178</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15530,34 +15530,34 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="W123" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X123" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AA123" t="n">
         <v>5</v>
@@ -15565,17 +15565,17 @@
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15617,7 @@
         <v>4025</v>
       </c>
       <c r="G124" t="n">
-        <v>9030</v>
+        <v>9027</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -15671,16 +15671,16 @@
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="X124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AA124" t="n">
         <v>5</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15740,7 +15740,7 @@
         <v>4025</v>
       </c>
       <c r="G125" t="n">
-        <v>9044</v>
+        <v>9030</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -15794,16 +15794,16 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA125" t="n">
         <v>5</v>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15860,19 +15860,19 @@
         <v>422</v>
       </c>
       <c r="F126" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G126" t="n">
-        <v>4327</v>
+        <v>9044</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15914,19 +15914,19 @@
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="AA126" t="n">
         <v>5</v>
@@ -15934,17 +15934,17 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         <v>4026</v>
       </c>
       <c r="G127" t="n">
-        <v>4334</v>
+        <v>4327</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -16022,34 +16022,34 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>3469273</v>
+        <v>11949</v>
       </c>
       <c r="W127" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="X127" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AA127" t="n">
         <v>5</v>
@@ -16062,12 +16062,12 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -16145,34 +16145,34 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>5374</v>
+        <v>3469273</v>
       </c>
       <c r="W128" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="X128" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AA128" t="n">
         <v>5</v>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -16283,19 +16283,19 @@
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="W129" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="X129" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AA129" t="n">
         <v>5</v>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -16391,7 +16391,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -16400,25 +16400,25 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="W130" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="X130" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AA130" t="n">
         <v>5</v>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -16514,7 +16514,7 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>225</v>
+        <v>4890595.9</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -16523,25 +16523,25 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>225</v>
+        <v>4890595.9</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="W131" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AA131" t="n">
         <v>5</v>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16601,21 +16601,21 @@
         <v>4026</v>
       </c>
       <c r="G132" t="n">
-        <v>9025</v>
+        <v>4334</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -16637,7 +16637,7 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -16646,25 +16646,25 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W132" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="X132" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Y132" t="n">
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="AA132" t="n">
         <v>5</v>
@@ -16672,27 +16672,27 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16718,22 +16718,22 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F133" t="n">
         <v>4026</v>
       </c>
       <c r="G133" t="n">
-        <v>4322</v>
+        <v>9025</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16775,19 +16775,19 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>7143</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="X133" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="AA133" t="n">
         <v>5</v>
@@ -16795,17 +16795,17 @@
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -16892,25 +16892,25 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>33669</v>
+        <v>7143</v>
       </c>
       <c r="W134" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="X134" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AA134" t="n">
         <v>5</v>
@@ -16923,12 +16923,12 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -16970,16 +16970,16 @@
         <v>4026</v>
       </c>
       <c r="G135" t="n">
-        <v>9234</v>
+        <v>4322</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -17006,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -17015,25 +17015,25 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="W135" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="X135" t="n">
-        <v>100000</v>
+        <v>187297</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="AA135" t="n">
         <v>5</v>
@@ -17041,17 +17041,17 @@
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17087,22 +17087,22 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F136" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G136" t="n">
-        <v>4426</v>
+        <v>9234</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -17147,16 +17147,16 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="X136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="AA136" t="n">
         <v>5</v>
@@ -17164,17 +17164,17 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -17184,48 +17184,48 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F137" t="n">
         <v>4010</v>
       </c>
       <c r="G137" t="n">
-        <v>4302</v>
+        <v>4426</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -17234,7 +17234,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>3235052.09</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -17243,7 +17243,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3235052.09</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -17252,34 +17252,34 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="X137" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AA137" t="n">
         <v>5</v>
@@ -17292,12 +17292,12 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>3235052.09</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -17366,7 +17366,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3235052.09</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -17375,34 +17375,34 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="W138" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="X138" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AA138" t="n">
         <v>5</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -17452,21 +17452,21 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F139" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G139" t="n">
-        <v>3002</v>
+        <v>4302</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -17513,19 +17513,19 @@
         <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="W139" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AA139" t="n">
         <v>5</v>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -17579,13 +17579,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F140" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G140" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>438463.7</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -17615,40 +17615,40 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>16556247.06</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>133336049.87</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>103758007.13</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>106566937.33</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>116779802.81</v>
+        <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>2808930.2</v>
+        <v>0</v>
       </c>
       <c r="V140" t="n">
-        <v>166077092</v>
+        <v>1000</v>
       </c>
       <c r="W140" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="X140" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="AA140" t="n">
         <v>5</v>
@@ -17661,12 +17661,12 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -17717,16 +17717,16 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>438463.7</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17738,40 +17738,40 @@
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>16556247.06</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>133336049.87</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>103758007.13</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>106566937.33</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>116779802.81</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>2808930.2</v>
       </c>
       <c r="V141" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="W141" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AA141" t="n">
         <v>5</v>
@@ -17784,22 +17784,22 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="W142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X142" t="n">
         <v>0</v>
@@ -17894,7 +17894,7 @@
         <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AA142" t="n">
         <v>5</v>
@@ -17907,7 +17907,7 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
@@ -17917,12 +17917,12 @@
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -17963,16 +17963,16 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -17984,40 +17984,40 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>52634438.4</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="W143" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="X143" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AA143" t="n">
         <v>5</v>
@@ -18030,22 +18030,22 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>5410565.4</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -18107,40 +18107,40 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>180000</v>
+        <v>26317219.2</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>31750960.63</v>
+        <v>52634438.4</v>
       </c>
       <c r="R144" t="n">
-        <v>31570960.63</v>
+        <v>26317219.2</v>
       </c>
       <c r="S144" t="n">
-        <v>31570960.63</v>
+        <v>26317219.2</v>
       </c>
       <c r="T144" t="n">
-        <v>31570960.63</v>
+        <v>26317219.2</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>80849746</v>
+        <v>136889022</v>
       </c>
       <c r="W144" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="X144" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="AA144" t="n">
         <v>5</v>
@@ -18153,12 +18153,12 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -18230,40 +18230,40 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>31750960.63</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>31570960.63</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>31570960.63</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>31570960.63</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>2000</v>
+        <v>80849746</v>
       </c>
       <c r="W145" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="X145" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Y145" t="n">
         <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="AA145" t="n">
         <v>5</v>
@@ -18276,7 +18276,7 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
@@ -18286,24 +18286,24 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -18317,27 +18317,27 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F146" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G146" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -18374,10 +18374,10 @@
         <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="W146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -18386,7 +18386,7 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AA146" t="n">
         <v>5</v>
@@ -18394,39 +18394,39 @@
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -18440,22 +18440,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F147" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G147" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18497,10 +18497,10 @@
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>6245</v>
+        <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>6245</v>
+        <v>0</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>6245</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -18517,17 +18517,17 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -18563,22 +18563,22 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F148" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G148" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -18620,10 +18620,10 @@
         <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="W148" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="AA148" t="n">
         <v>5</v>
@@ -18640,17 +18640,17 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -18686,27 +18686,27 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F149" t="n">
-        <v>4019</v>
+        <v>4004</v>
       </c>
       <c r="G149" t="n">
-        <v>6160</v>
+        <v>2803</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -18743,10 +18743,10 @@
         <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>6245</v>
       </c>
       <c r="AA149" t="n">
         <v>5</v>
@@ -18763,27 +18763,27 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>04/02/2026 15:36:37</t>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
@@ -18809,31 +18809,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F150" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G150" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>1433738.57</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -18842,34 +18842,34 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>127680</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>35187195.47</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>31855789.6</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>33468553.7</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>32118763.49</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="W150" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>61292510</v>
+        <v>1000</v>
       </c>
       <c r="AA150" t="n">
         <v>5</v>
@@ -18886,27 +18886,273 @@
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
+          <t>Tecnologia</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>DTIC - Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>19/02/2026 15:04:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>422</v>
+      </c>
+      <c r="F151" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G151" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr">
+        <is>
           <t>Criança e Adolescente</t>
         </is>
       </c>
-      <c r="AD150" t="inlineStr">
+      <c r="AD151" t="inlineStr">
         <is>
           <t>FUMCAD</t>
         </is>
       </c>
-      <c r="AE150" t="inlineStr">
+      <c r="AE151" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AF150" t="inlineStr">
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>19/02/2026 15:04:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>422</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G152" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>1433738.57</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>127680</v>
+      </c>
+      <c r="O152" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>35187195.47</v>
+      </c>
+      <c r="R152" t="n">
+        <v>31855789.6</v>
+      </c>
+      <c r="S152" t="n">
+        <v>33468553.7</v>
+      </c>
+      <c r="T152" t="n">
+        <v>32118763.49</v>
+      </c>
+      <c r="U152" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="V152" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="W152" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
         <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>04/02/2026 15:36:37</t>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>19/02/2026 15:04:36</t>
         </is>
       </c>
     </row>
